--- a/CSharp/SpreadSheetAsDataのテスト/TestData/テーブル.xlsx
+++ b/CSharp/SpreadSheetAsDataのテスト/TestData/テーブル.xlsx
@@ -324,6 +324,17 @@
     <tableColumn id="3" name="string"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="空白数値マッピング" displayName="空白数値マッピング" ref="M1:N3" totalsRowShown="0">
+  <autoFilter ref="M1:N3"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="行"/>
+    <tableColumn id="2" name="数値"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -614,10 +625,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -627,8 +638,14 @@
       <c r="C1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="M1" t="str">
+        <v>行</v>
+      </c>
+      <c r="N1" t="str">
+        <v>数値</v>
+      </c>
+    </row>
+    <row r="2" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>1.1000000000000001</v>
       </c>
@@ -638,8 +655,14 @@
       <c r="C2" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>2.2000000000000002</v>
       </c>
@@ -648,6 +671,9 @@
       </c>
       <c r="C3" t="b">
         <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.15">
@@ -756,140 +782,6 @@
       </c>
       <c r="E9" t="b">
         <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="3">
-    <tablePart r:id="rId1"/>
-    <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H36"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="G11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B23" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B25">
-        <v>2</v>
-      </c>
-      <c r="C25">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B26">
-        <v>3</v>
-      </c>
-      <c r="C26">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B27">
-        <v>4</v>
-      </c>
-      <c r="C27">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="C32" t="s">
-        <v>28</v>
-      </c>
-      <c r="D32" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="3:6" x14ac:dyDescent="0.15">
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33">
-        <v>5</v>
-      </c>
-      <c r="F33" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" spans="3:6" x14ac:dyDescent="0.15">
-      <c r="C34">
-        <v>2</v>
-      </c>
-      <c r="D34">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="3:6" x14ac:dyDescent="0.15">
-      <c r="C35">
-        <v>3</v>
-      </c>
-      <c r="D35">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="3:6" x14ac:dyDescent="0.15">
-      <c r="C36">
-        <v>4</v>
-      </c>
-      <c r="D36">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -904,6 +796,141 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H36"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="G11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <v>6</v>
+      </c>
+      <c r="F25" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B27">
+        <v>4</v>
+      </c>
+      <c r="C27">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C32" t="s">
+        <v>28</v>
+      </c>
+      <c r="D32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="3:6" x14ac:dyDescent="0.15">
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>5</v>
+      </c>
+      <c r="F33" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="3:6" x14ac:dyDescent="0.15">
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="3:6" x14ac:dyDescent="0.15">
+      <c r="C35">
+        <v>3</v>
+      </c>
+      <c r="D35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="3:6" x14ac:dyDescent="0.15">
+      <c r="C36">
+        <v>4</v>
+      </c>
+      <c r="D36">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="4">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C12"/>

--- a/CSharp/SpreadSheetAsDataのテスト/TestData/テーブル.xlsx
+++ b/CSharp/SpreadSheetAsDataのテスト/TestData/テーブル.xlsx
@@ -328,11 +328,12 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="空白数値マッピング" displayName="空白数値マッピング" ref="M1:N3" totalsRowShown="0">
-  <autoFilter ref="M1:N3"/>
-  <tableColumns count="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="空白数値マッピング" displayName="空白数値マッピング" ref="M1:O3" totalsRowShown="0">
+  <autoFilter ref="M1:O3"/>
+  <tableColumns count="3">
     <tableColumn id="1" name="行"/>
     <tableColumn id="2" name="数値"/>
+    <tableColumn id="3" name="真偽値"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -625,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" x14ac:dyDescent="0.15">
@@ -644,6 +645,9 @@
       <c r="N1" t="str">
         <v>数値</v>
       </c>
+      <c r="O1" t="str">
+        <v>真偽値</v>
+      </c>
     </row>
     <row r="2" x14ac:dyDescent="0.15">
       <c r="A2">
@@ -659,6 +663,9 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
         <v>0</v>
       </c>
     </row>

--- a/CSharp/SpreadSheetAsDataのテスト/TestData/テーブル.xlsx
+++ b/CSharp/SpreadSheetAsDataのテスト/TestData/テーブル.xlsx
@@ -328,12 +328,13 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="空白数値マッピング" displayName="空白数値マッピング" ref="M1:O3" totalsRowShown="0">
-  <autoFilter ref="M1:O3"/>
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="空白数値マッピング" displayName="空白数値マッピング" ref="M1:P3" totalsRowShown="0">
+  <autoFilter ref="M1:P3"/>
+  <tableColumns count="4">
     <tableColumn id="1" name="行"/>
     <tableColumn id="2" name="数値"/>
     <tableColumn id="3" name="真偽値"/>
+    <tableColumn id="4" name="小数"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -626,7 +627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" x14ac:dyDescent="0.15">
@@ -648,6 +649,9 @@
       <c r="O1" t="str">
         <v>真偽値</v>
       </c>
+      <c r="P1" t="str">
+        <v>小数</v>
+      </c>
     </row>
     <row r="2" x14ac:dyDescent="0.15">
       <c r="A2">
@@ -667,6 +671,9 @@
       </c>
       <c r="O2" t="b">
         <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="3" x14ac:dyDescent="0.15">
